--- a/B-Sides 2026/B-Sides 2026/b-sides-2026-cpl.xlsx
+++ b/B-Sides 2026/B-Sides 2026/b-sides-2026-cpl.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="78">
   <si>
     <t xml:space="preserve">Designator</t>
   </si>
@@ -82,30 +82,30 @@
     <t xml:space="preserve">C3</t>
   </si>
   <si>
+    <t xml:space="preserve">82.5000mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-62.0000mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.2800mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-70.3800mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5</t>
+  </si>
+  <si>
     <t xml:space="preserve">97.5400mm</t>
   </si>
   <si>
     <t xml:space="preserve">-57.0000mm</t>
   </si>
   <si>
-    <t xml:space="preserve">C4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.2800mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-70.3800mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5000mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-62.0000mm</t>
-  </si>
-  <si>
     <t xml:space="preserve">C6</t>
   </si>
   <si>
@@ -218,6 +218,42 @@
   </si>
   <si>
     <t xml:space="preserve">-56.7600mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.7337mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-47.1988mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bottom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0062mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-65.6188mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.0063mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-48.3812mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.2337mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-70.8012mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5000mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-61.0000mm</t>
   </si>
 </sst>
 </file>
@@ -227,7 +263,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,13 +300,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -345,7 +374,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -538,11 +567,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="8.890625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.4" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.11"/>
@@ -649,6 +678,8 @@
       <c r="E6" s="3" t="n">
         <v>90</v>
       </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
@@ -666,6 +697,8 @@
       <c r="E7" s="3" t="n">
         <v>-90</v>
       </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
@@ -692,7 +725,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
@@ -905,15 +938,90 @@
         <v>180</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="4"/>
+    <row r="22" s="4" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="23" s="4" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" s="4" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>-120</v>
+      </c>
+    </row>
+    <row r="26" s="4" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
